--- a/public/exports-60-250/29188475.xlsx
+++ b/public/exports-60-250/29188475.xlsx
@@ -2539,7 +2539,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526272</t>
+          <t xml:space="preserve">311526269</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562922</t>
+          <t xml:space="preserve">311562921</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562932</t>
+          <t xml:space="preserve">311562929</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562925</t>
+          <t xml:space="preserve">311562921</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M59" t="inlineStr">
